--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:13</t>
+    <t xml:space="preserve">2026-09-09 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:07</t>
+    <t xml:space="preserve">2026-09-17 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:03</t>
+    <t xml:space="preserve">2026-09-23 12:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:32</t>
+    <t xml:space="preserve">2026-10-02 13:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:25</t>
+    <t xml:space="preserve">2026-10-04 08:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:57</t>
+    <t xml:space="preserve">2026-10-05 10:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -677,7 +677,7 @@
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>296310.62</v>
+        <v>296310.63</v>
       </c>
     </row>
     <row r="8">
@@ -915,7 +915,7 @@
         <v>2018</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>236730.12</v>
+        <v>236730.13</v>
       </c>
     </row>
     <row r="22">
@@ -949,7 +949,7 @@
         <v>2018</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>232948.12</v>
+        <v>232948.13</v>
       </c>
     </row>
     <row r="24">
@@ -1068,7 +1068,7 @@
         <v>2018</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>199391.12</v>
+        <v>199391.13</v>
       </c>
     </row>
     <row r="31">
